--- a/Flat_Master_List.xlsx
+++ b/Flat_Master_List.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="758">
   <si>
     <t>S.No.</t>
   </si>
@@ -216,9 +216,6 @@
     <t>A-804</t>
   </si>
   <si>
-    <t>A-805</t>
-  </si>
-  <si>
     <t>A-806</t>
   </si>
   <si>
@@ -312,9 +309,6 @@
     <t>A-1204</t>
   </si>
   <si>
-    <t>A-1205</t>
-  </si>
-  <si>
     <t>A-1206</t>
   </si>
   <si>
@@ -645,9 +639,6 @@
     <t>B-806</t>
   </si>
   <si>
-    <t>B-807</t>
-  </si>
-  <si>
     <t>B-808</t>
   </si>
   <si>
@@ -789,9 +780,6 @@
     <t>B-1206</t>
   </si>
   <si>
-    <t>B-1207</t>
-  </si>
-  <si>
     <t>B-1208</t>
   </si>
   <si>
@@ -1152,9 +1140,6 @@
     <t>C-806</t>
   </si>
   <si>
-    <t>C-807</t>
-  </si>
-  <si>
     <t>C-808</t>
   </si>
   <si>
@@ -1296,9 +1281,6 @@
     <t>C-1206</t>
   </si>
   <si>
-    <t>C-1207</t>
-  </si>
-  <si>
     <t>C-1208</t>
   </si>
   <si>
@@ -1512,9 +1494,6 @@
     <t>D1-705</t>
   </si>
   <si>
-    <t>D1-706</t>
-  </si>
-  <si>
     <t>D1-801</t>
   </si>
   <si>
@@ -1584,9 +1563,6 @@
     <t>D1-1105</t>
   </si>
   <si>
-    <t>D1-1106</t>
-  </si>
-  <si>
     <t>D1-1201</t>
   </si>
   <si>
@@ -1743,9 +1719,6 @@
     <t>D2-703</t>
   </si>
   <si>
-    <t>D2-704</t>
-  </si>
-  <si>
     <t>D2-705</t>
   </si>
   <si>
@@ -1815,9 +1788,6 @@
     <t>D2-1103</t>
   </si>
   <si>
-    <t>D2-1104</t>
-  </si>
-  <si>
     <t>D2-1105</t>
   </si>
   <si>
@@ -2043,9 +2013,6 @@
     <t>E-804</t>
   </si>
   <si>
-    <t>E-805</t>
-  </si>
-  <si>
     <t>E-806</t>
   </si>
   <si>
@@ -2137,9 +2104,6 @@
   </si>
   <si>
     <t>E-1204</t>
-  </si>
-  <si>
-    <t>E-1205</t>
   </si>
   <si>
     <t>E-1206</t>
@@ -2725,7 +2689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E759"/>
+  <dimension ref="A1:E747"/>
   <sheetFormatPr defaultColWidth="31" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4183,7 +4147,7 @@
         <v>116</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>6</v>
+        <v>117</v>
       </c>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -4193,10 +4157,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>6</v>
+        <v>117</v>
       </c>
       <c r="D113" s="5"/>
       <c r="E113" s="5"/>
@@ -4206,10 +4170,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -4222,7 +4186,7 @@
         <v>120</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D115" s="5"/>
       <c r="E115" s="5"/>
@@ -4235,7 +4199,7 @@
         <v>121</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -4248,7 +4212,7 @@
         <v>122</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D117" s="5"/>
       <c r="E117" s="5"/>
@@ -4261,7 +4225,7 @@
         <v>123</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -4274,7 +4238,7 @@
         <v>124</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D119" s="5"/>
       <c r="E119" s="5"/>
@@ -4287,7 +4251,7 @@
         <v>125</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -4300,7 +4264,7 @@
         <v>126</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D121" s="5"/>
       <c r="E121" s="5"/>
@@ -4313,7 +4277,7 @@
         <v>127</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -4326,7 +4290,7 @@
         <v>128</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D123" s="5"/>
       <c r="E123" s="5"/>
@@ -4339,7 +4303,7 @@
         <v>129</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -4352,7 +4316,7 @@
         <v>130</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D125" s="5"/>
       <c r="E125" s="5"/>
@@ -4365,7 +4329,7 @@
         <v>131</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -4378,7 +4342,7 @@
         <v>132</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D127" s="5"/>
       <c r="E127" s="5"/>
@@ -4391,7 +4355,7 @@
         <v>133</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -4404,7 +4368,7 @@
         <v>134</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D129" s="5"/>
       <c r="E129" s="5"/>
@@ -4417,7 +4381,7 @@
         <v>135</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -4430,7 +4394,7 @@
         <v>136</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D131" s="5"/>
       <c r="E131" s="5"/>
@@ -4443,7 +4407,7 @@
         <v>137</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -4456,7 +4420,7 @@
         <v>138</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D133" s="5"/>
       <c r="E133" s="5"/>
@@ -4469,7 +4433,7 @@
         <v>139</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -4482,7 +4446,7 @@
         <v>140</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D135" s="5"/>
       <c r="E135" s="5"/>
@@ -4495,7 +4459,7 @@
         <v>141</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -4508,7 +4472,7 @@
         <v>142</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D137" s="5"/>
       <c r="E137" s="5"/>
@@ -4521,7 +4485,7 @@
         <v>143</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -4534,7 +4498,7 @@
         <v>144</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D139" s="5"/>
       <c r="E139" s="5"/>
@@ -4547,7 +4511,7 @@
         <v>145</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -4560,7 +4524,7 @@
         <v>146</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D141" s="5"/>
       <c r="E141" s="5"/>
@@ -4573,7 +4537,7 @@
         <v>147</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -4586,7 +4550,7 @@
         <v>148</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D143" s="5"/>
       <c r="E143" s="5"/>
@@ -4599,7 +4563,7 @@
         <v>149</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -4612,7 +4576,7 @@
         <v>150</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D145" s="5"/>
       <c r="E145" s="5"/>
@@ -4625,7 +4589,7 @@
         <v>151</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -4638,7 +4602,7 @@
         <v>152</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D147" s="5"/>
       <c r="E147" s="5"/>
@@ -4651,7 +4615,7 @@
         <v>153</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -4664,7 +4628,7 @@
         <v>154</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D149" s="5"/>
       <c r="E149" s="5"/>
@@ -4677,7 +4641,7 @@
         <v>155</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -4690,7 +4654,7 @@
         <v>156</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D151" s="5"/>
       <c r="E151" s="5"/>
@@ -4703,7 +4667,7 @@
         <v>157</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -4716,7 +4680,7 @@
         <v>158</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D153" s="5"/>
       <c r="E153" s="5"/>
@@ -4729,7 +4693,7 @@
         <v>159</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -4742,7 +4706,7 @@
         <v>160</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D155" s="5"/>
       <c r="E155" s="5"/>
@@ -4755,7 +4719,7 @@
         <v>161</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -4768,7 +4732,7 @@
         <v>162</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5"/>
@@ -4781,7 +4745,7 @@
         <v>163</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -4794,7 +4758,7 @@
         <v>164</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D159" s="5"/>
       <c r="E159" s="5"/>
@@ -4807,7 +4771,7 @@
         <v>165</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -4820,7 +4784,7 @@
         <v>166</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D161" s="5"/>
       <c r="E161" s="5"/>
@@ -4833,7 +4797,7 @@
         <v>167</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -4846,7 +4810,7 @@
         <v>168</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D163" s="5"/>
       <c r="E163" s="5"/>
@@ -4859,7 +4823,7 @@
         <v>169</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -4872,7 +4836,7 @@
         <v>170</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D165" s="5"/>
       <c r="E165" s="5"/>
@@ -4885,7 +4849,7 @@
         <v>171</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -4898,7 +4862,7 @@
         <v>172</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D167" s="5"/>
       <c r="E167" s="5"/>
@@ -4911,7 +4875,7 @@
         <v>173</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -4924,7 +4888,7 @@
         <v>174</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D169" s="5"/>
       <c r="E169" s="5"/>
@@ -4937,7 +4901,7 @@
         <v>175</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -4950,7 +4914,7 @@
         <v>176</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D171" s="5"/>
       <c r="E171" s="5"/>
@@ -4963,7 +4927,7 @@
         <v>177</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -4976,7 +4940,7 @@
         <v>178</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D173" s="5"/>
       <c r="E173" s="5"/>
@@ -4989,7 +4953,7 @@
         <v>179</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -5002,7 +4966,7 @@
         <v>180</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D175" s="5"/>
       <c r="E175" s="5"/>
@@ -5015,7 +4979,7 @@
         <v>181</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -5028,7 +4992,7 @@
         <v>182</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D177" s="5"/>
       <c r="E177" s="5"/>
@@ -5041,7 +5005,7 @@
         <v>183</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -5054,7 +5018,7 @@
         <v>184</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D179" s="5"/>
       <c r="E179" s="5"/>
@@ -5067,7 +5031,7 @@
         <v>185</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -5080,7 +5044,7 @@
         <v>186</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D181" s="5"/>
       <c r="E181" s="5"/>
@@ -5093,7 +5057,7 @@
         <v>187</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -5106,7 +5070,7 @@
         <v>188</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D183" s="5"/>
       <c r="E183" s="5"/>
@@ -5119,7 +5083,7 @@
         <v>189</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -5132,7 +5096,7 @@
         <v>190</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D185" s="5"/>
       <c r="E185" s="5"/>
@@ -5145,7 +5109,7 @@
         <v>191</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -5158,7 +5122,7 @@
         <v>192</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D187" s="5"/>
       <c r="E187" s="5"/>
@@ -5171,7 +5135,7 @@
         <v>193</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -5184,7 +5148,7 @@
         <v>194</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D189" s="5"/>
       <c r="E189" s="5"/>
@@ -5197,7 +5161,7 @@
         <v>195</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -5210,7 +5174,7 @@
         <v>196</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D191" s="5"/>
       <c r="E191" s="5"/>
@@ -5223,7 +5187,7 @@
         <v>197</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -5236,7 +5200,7 @@
         <v>198</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D193" s="5"/>
       <c r="E193" s="5"/>
@@ -5249,7 +5213,7 @@
         <v>199</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -5262,7 +5226,7 @@
         <v>200</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D195" s="5"/>
       <c r="E195" s="5"/>
@@ -5275,7 +5239,7 @@
         <v>201</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -5288,7 +5252,7 @@
         <v>202</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D197" s="5"/>
       <c r="E197" s="5"/>
@@ -5301,7 +5265,7 @@
         <v>203</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -5314,7 +5278,7 @@
         <v>204</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D199" s="5"/>
       <c r="E199" s="5"/>
@@ -5327,7 +5291,7 @@
         <v>205</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -5340,7 +5304,7 @@
         <v>206</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D201" s="5"/>
       <c r="E201" s="5"/>
@@ -5353,7 +5317,7 @@
         <v>207</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -5366,7 +5330,7 @@
         <v>208</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D203" s="5"/>
       <c r="E203" s="5"/>
@@ -5379,7 +5343,7 @@
         <v>209</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -5392,7 +5356,7 @@
         <v>210</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D205" s="5"/>
       <c r="E205" s="5"/>
@@ -5405,7 +5369,7 @@
         <v>211</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -5418,7 +5382,7 @@
         <v>212</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D207" s="5"/>
       <c r="E207" s="5"/>
@@ -5431,7 +5395,7 @@
         <v>213</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -5444,7 +5408,7 @@
         <v>214</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D209" s="5"/>
       <c r="E209" s="5"/>
@@ -5457,7 +5421,7 @@
         <v>215</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -5470,7 +5434,7 @@
         <v>216</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D211" s="5"/>
       <c r="E211" s="5"/>
@@ -5483,7 +5447,7 @@
         <v>217</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -5496,7 +5460,7 @@
         <v>218</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D213" s="5"/>
       <c r="E213" s="5"/>
@@ -5509,7 +5473,7 @@
         <v>219</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -5522,7 +5486,7 @@
         <v>220</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D215" s="5"/>
       <c r="E215" s="5"/>
@@ -5535,7 +5499,7 @@
         <v>221</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -5548,7 +5512,7 @@
         <v>222</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D217" s="5"/>
       <c r="E217" s="5"/>
@@ -5561,7 +5525,7 @@
         <v>223</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -5574,7 +5538,7 @@
         <v>224</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D219" s="5"/>
       <c r="E219" s="5"/>
@@ -5587,7 +5551,7 @@
         <v>225</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -5600,7 +5564,7 @@
         <v>226</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D221" s="5"/>
       <c r="E221" s="5"/>
@@ -5613,7 +5577,7 @@
         <v>227</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -5626,7 +5590,7 @@
         <v>228</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D223" s="5"/>
       <c r="E223" s="5"/>
@@ -5639,7 +5603,7 @@
         <v>229</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -5652,7 +5616,7 @@
         <v>230</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D225" s="5"/>
       <c r="E225" s="5"/>
@@ -5665,7 +5629,7 @@
         <v>231</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -5678,7 +5642,7 @@
         <v>232</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D227" s="5"/>
       <c r="E227" s="5"/>
@@ -5691,7 +5655,7 @@
         <v>233</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -5704,7 +5668,7 @@
         <v>234</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D229" s="5"/>
       <c r="E229" s="5"/>
@@ -5717,7 +5681,7 @@
         <v>235</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -5730,7 +5694,7 @@
         <v>236</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D231" s="5"/>
       <c r="E231" s="5"/>
@@ -5743,7 +5707,7 @@
         <v>237</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -5756,7 +5720,7 @@
         <v>238</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D233" s="5"/>
       <c r="E233" s="5"/>
@@ -5769,7 +5733,7 @@
         <v>239</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -5782,7 +5746,7 @@
         <v>240</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D235" s="5"/>
       <c r="E235" s="5"/>
@@ -5795,7 +5759,7 @@
         <v>241</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -5808,7 +5772,7 @@
         <v>242</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D237" s="5"/>
       <c r="E237" s="5"/>
@@ -5821,7 +5785,7 @@
         <v>243</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -5834,7 +5798,7 @@
         <v>244</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D239" s="5"/>
       <c r="E239" s="5"/>
@@ -5847,7 +5811,7 @@
         <v>245</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -5860,7 +5824,7 @@
         <v>246</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D241" s="5"/>
       <c r="E241" s="5"/>
@@ -5873,7 +5837,7 @@
         <v>247</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -5886,7 +5850,7 @@
         <v>248</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D243" s="5"/>
       <c r="E243" s="5"/>
@@ -5899,7 +5863,7 @@
         <v>249</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -5912,7 +5876,7 @@
         <v>250</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D245" s="5"/>
       <c r="E245" s="5"/>
@@ -5925,7 +5889,7 @@
         <v>251</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -5938,7 +5902,7 @@
         <v>252</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D247" s="5"/>
       <c r="E247" s="5"/>
@@ -5951,7 +5915,7 @@
         <v>253</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -5964,7 +5928,7 @@
         <v>254</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D249" s="5"/>
       <c r="E249" s="5"/>
@@ -5977,7 +5941,7 @@
         <v>255</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -5990,7 +5954,7 @@
         <v>256</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D251" s="5"/>
       <c r="E251" s="5"/>
@@ -6003,7 +5967,7 @@
         <v>257</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -6016,7 +5980,7 @@
         <v>258</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D253" s="5"/>
       <c r="E253" s="5"/>
@@ -6029,7 +5993,7 @@
         <v>259</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -6042,7 +6006,7 @@
         <v>260</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D255" s="5"/>
       <c r="E255" s="5"/>
@@ -6055,7 +6019,7 @@
         <v>261</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -6068,7 +6032,7 @@
         <v>262</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D257" s="5"/>
       <c r="E257" s="5"/>
@@ -6081,7 +6045,7 @@
         <v>263</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -6094,7 +6058,7 @@
         <v>264</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D259" s="5"/>
       <c r="E259" s="5"/>
@@ -6107,7 +6071,7 @@
         <v>265</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -6120,7 +6084,7 @@
         <v>266</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D261" s="5"/>
       <c r="E261" s="5"/>
@@ -6133,7 +6097,7 @@
         <v>267</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -6146,7 +6110,7 @@
         <v>268</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D263" s="5"/>
       <c r="E263" s="5"/>
@@ -6159,7 +6123,7 @@
         <v>269</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -6172,7 +6136,7 @@
         <v>270</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D265" s="5"/>
       <c r="E265" s="5"/>
@@ -6185,7 +6149,7 @@
         <v>271</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -6198,7 +6162,7 @@
         <v>272</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D267" s="5"/>
       <c r="E267" s="5"/>
@@ -6211,7 +6175,7 @@
         <v>273</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -6224,7 +6188,7 @@
         <v>274</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D269" s="5"/>
       <c r="E269" s="5"/>
@@ -6237,7 +6201,7 @@
         <v>275</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -6250,7 +6214,7 @@
         <v>276</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D271" s="5"/>
       <c r="E271" s="5"/>
@@ -6263,7 +6227,7 @@
         <v>277</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -6276,7 +6240,7 @@
         <v>278</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D273" s="5"/>
       <c r="E273" s="5"/>
@@ -6289,7 +6253,7 @@
         <v>279</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -6302,7 +6266,7 @@
         <v>280</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D275" s="5"/>
       <c r="E275" s="5"/>
@@ -6315,7 +6279,7 @@
         <v>281</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -6328,7 +6292,7 @@
         <v>282</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D277" s="5"/>
       <c r="E277" s="5"/>
@@ -6341,7 +6305,7 @@
         <v>283</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>119</v>
+        <v>284</v>
       </c>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -6351,10 +6315,10 @@
         <v>278</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>119</v>
+        <v>284</v>
       </c>
       <c r="D279" s="5"/>
       <c r="E279" s="5"/>
@@ -6364,10 +6328,10 @@
         <v>279</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>119</v>
+        <v>284</v>
       </c>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -6377,10 +6341,10 @@
         <v>280</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>119</v>
+        <v>284</v>
       </c>
       <c r="D281" s="5"/>
       <c r="E281" s="5"/>
@@ -6390,10 +6354,10 @@
         <v>281</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D282" s="3"/>
       <c r="E282" s="3"/>
@@ -6406,7 +6370,7 @@
         <v>289</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D283" s="5"/>
       <c r="E283" s="5"/>
@@ -6419,7 +6383,7 @@
         <v>290</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
@@ -6432,7 +6396,7 @@
         <v>291</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D285" s="5"/>
       <c r="E285" s="5"/>
@@ -6445,7 +6409,7 @@
         <v>292</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D286" s="3"/>
       <c r="E286" s="3"/>
@@ -6458,7 +6422,7 @@
         <v>293</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D287" s="5"/>
       <c r="E287" s="5"/>
@@ -6471,7 +6435,7 @@
         <v>294</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D288" s="3"/>
       <c r="E288" s="3"/>
@@ -6484,7 +6448,7 @@
         <v>295</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D289" s="5"/>
       <c r="E289" s="5"/>
@@ -6497,7 +6461,7 @@
         <v>296</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D290" s="3"/>
       <c r="E290" s="3"/>
@@ -6510,7 +6474,7 @@
         <v>297</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D291" s="5"/>
       <c r="E291" s="5"/>
@@ -6523,7 +6487,7 @@
         <v>298</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D292" s="3"/>
       <c r="E292" s="3"/>
@@ -6536,7 +6500,7 @@
         <v>299</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D293" s="5"/>
       <c r="E293" s="5"/>
@@ -6549,7 +6513,7 @@
         <v>300</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D294" s="3"/>
       <c r="E294" s="3"/>
@@ -6562,7 +6526,7 @@
         <v>301</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D295" s="5"/>
       <c r="E295" s="5"/>
@@ -6575,7 +6539,7 @@
         <v>302</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D296" s="3"/>
       <c r="E296" s="3"/>
@@ -6588,7 +6552,7 @@
         <v>303</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D297" s="5"/>
       <c r="E297" s="5"/>
@@ -6601,7 +6565,7 @@
         <v>304</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D298" s="3"/>
       <c r="E298" s="3"/>
@@ -6614,7 +6578,7 @@
         <v>305</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D299" s="5"/>
       <c r="E299" s="5"/>
@@ -6627,7 +6591,7 @@
         <v>306</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D300" s="3"/>
       <c r="E300" s="3"/>
@@ -6640,7 +6604,7 @@
         <v>307</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D301" s="5"/>
       <c r="E301" s="5"/>
@@ -6653,7 +6617,7 @@
         <v>308</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D302" s="3"/>
       <c r="E302" s="3"/>
@@ -6666,7 +6630,7 @@
         <v>309</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D303" s="5"/>
       <c r="E303" s="5"/>
@@ -6679,7 +6643,7 @@
         <v>310</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D304" s="3"/>
       <c r="E304" s="3"/>
@@ -6692,7 +6656,7 @@
         <v>311</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D305" s="5"/>
       <c r="E305" s="5"/>
@@ -6705,7 +6669,7 @@
         <v>312</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D306" s="3"/>
       <c r="E306" s="3"/>
@@ -6718,7 +6682,7 @@
         <v>313</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D307" s="5"/>
       <c r="E307" s="5"/>
@@ -6731,7 +6695,7 @@
         <v>314</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D308" s="3"/>
       <c r="E308" s="3"/>
@@ -6744,7 +6708,7 @@
         <v>315</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D309" s="5"/>
       <c r="E309" s="5"/>
@@ -6757,7 +6721,7 @@
         <v>316</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D310" s="3"/>
       <c r="E310" s="3"/>
@@ -6770,7 +6734,7 @@
         <v>317</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D311" s="5"/>
       <c r="E311" s="5"/>
@@ -6783,7 +6747,7 @@
         <v>318</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D312" s="3"/>
       <c r="E312" s="3"/>
@@ -6796,7 +6760,7 @@
         <v>319</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D313" s="5"/>
       <c r="E313" s="5"/>
@@ -6809,7 +6773,7 @@
         <v>320</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D314" s="3"/>
       <c r="E314" s="3"/>
@@ -6822,7 +6786,7 @@
         <v>321</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D315" s="5"/>
       <c r="E315" s="5"/>
@@ -6835,7 +6799,7 @@
         <v>322</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D316" s="3"/>
       <c r="E316" s="3"/>
@@ -6848,7 +6812,7 @@
         <v>323</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D317" s="5"/>
       <c r="E317" s="5"/>
@@ -6861,7 +6825,7 @@
         <v>324</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D318" s="3"/>
       <c r="E318" s="3"/>
@@ -6874,7 +6838,7 @@
         <v>325</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D319" s="5"/>
       <c r="E319" s="5"/>
@@ -6887,7 +6851,7 @@
         <v>326</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D320" s="3"/>
       <c r="E320" s="3"/>
@@ -6900,7 +6864,7 @@
         <v>327</v>
       </c>
       <c r="C321" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D321" s="5"/>
       <c r="E321" s="5"/>
@@ -6913,7 +6877,7 @@
         <v>328</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D322" s="3"/>
       <c r="E322" s="3"/>
@@ -6926,7 +6890,7 @@
         <v>329</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D323" s="5"/>
       <c r="E323" s="5"/>
@@ -6939,7 +6903,7 @@
         <v>330</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D324" s="3"/>
       <c r="E324" s="3"/>
@@ -6952,7 +6916,7 @@
         <v>331</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D325" s="5"/>
       <c r="E325" s="5"/>
@@ -6965,7 +6929,7 @@
         <v>332</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D326" s="3"/>
       <c r="E326" s="3"/>
@@ -6978,7 +6942,7 @@
         <v>333</v>
       </c>
       <c r="C327" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D327" s="5"/>
       <c r="E327" s="5"/>
@@ -6991,7 +6955,7 @@
         <v>334</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D328" s="3"/>
       <c r="E328" s="3"/>
@@ -7004,7 +6968,7 @@
         <v>335</v>
       </c>
       <c r="C329" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D329" s="5"/>
       <c r="E329" s="5"/>
@@ -7017,7 +6981,7 @@
         <v>336</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D330" s="3"/>
       <c r="E330" s="3"/>
@@ -7030,7 +6994,7 @@
         <v>337</v>
       </c>
       <c r="C331" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D331" s="5"/>
       <c r="E331" s="5"/>
@@ -7043,7 +7007,7 @@
         <v>338</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D332" s="3"/>
       <c r="E332" s="3"/>
@@ -7056,7 +7020,7 @@
         <v>339</v>
       </c>
       <c r="C333" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D333" s="5"/>
       <c r="E333" s="5"/>
@@ -7069,7 +7033,7 @@
         <v>340</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D334" s="3"/>
       <c r="E334" s="3"/>
@@ -7082,7 +7046,7 @@
         <v>341</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D335" s="5"/>
       <c r="E335" s="5"/>
@@ -7095,7 +7059,7 @@
         <v>342</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D336" s="3"/>
       <c r="E336" s="3"/>
@@ -7108,7 +7072,7 @@
         <v>343</v>
       </c>
       <c r="C337" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D337" s="5"/>
       <c r="E337" s="5"/>
@@ -7121,7 +7085,7 @@
         <v>344</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D338" s="3"/>
       <c r="E338" s="3"/>
@@ -7134,7 +7098,7 @@
         <v>345</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D339" s="5"/>
       <c r="E339" s="5"/>
@@ -7147,7 +7111,7 @@
         <v>346</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D340" s="3"/>
       <c r="E340" s="3"/>
@@ -7160,7 +7124,7 @@
         <v>347</v>
       </c>
       <c r="C341" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D341" s="5"/>
       <c r="E341" s="5"/>
@@ -7173,7 +7137,7 @@
         <v>348</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D342" s="3"/>
       <c r="E342" s="3"/>
@@ -7186,7 +7150,7 @@
         <v>349</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D343" s="5"/>
       <c r="E343" s="5"/>
@@ -7199,7 +7163,7 @@
         <v>350</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D344" s="3"/>
       <c r="E344" s="3"/>
@@ -7212,7 +7176,7 @@
         <v>351</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D345" s="5"/>
       <c r="E345" s="5"/>
@@ -7225,7 +7189,7 @@
         <v>352</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D346" s="3"/>
       <c r="E346" s="3"/>
@@ -7238,7 +7202,7 @@
         <v>353</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D347" s="5"/>
       <c r="E347" s="5"/>
@@ -7251,7 +7215,7 @@
         <v>354</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D348" s="3"/>
       <c r="E348" s="3"/>
@@ -7264,7 +7228,7 @@
         <v>355</v>
       </c>
       <c r="C349" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D349" s="5"/>
       <c r="E349" s="5"/>
@@ -7277,7 +7241,7 @@
         <v>356</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D350" s="3"/>
       <c r="E350" s="3"/>
@@ -7290,7 +7254,7 @@
         <v>357</v>
       </c>
       <c r="C351" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D351" s="5"/>
       <c r="E351" s="5"/>
@@ -7303,7 +7267,7 @@
         <v>358</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D352" s="3"/>
       <c r="E352" s="3"/>
@@ -7316,7 +7280,7 @@
         <v>359</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D353" s="5"/>
       <c r="E353" s="5"/>
@@ -7329,7 +7293,7 @@
         <v>360</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D354" s="3"/>
       <c r="E354" s="3"/>
@@ -7342,7 +7306,7 @@
         <v>361</v>
       </c>
       <c r="C355" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D355" s="5"/>
       <c r="E355" s="5"/>
@@ -7355,7 +7319,7 @@
         <v>362</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D356" s="3"/>
       <c r="E356" s="3"/>
@@ -7368,7 +7332,7 @@
         <v>363</v>
       </c>
       <c r="C357" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D357" s="5"/>
       <c r="E357" s="5"/>
@@ -7381,7 +7345,7 @@
         <v>364</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D358" s="3"/>
       <c r="E358" s="3"/>
@@ -7394,7 +7358,7 @@
         <v>365</v>
       </c>
       <c r="C359" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D359" s="5"/>
       <c r="E359" s="5"/>
@@ -7407,7 +7371,7 @@
         <v>366</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D360" s="3"/>
       <c r="E360" s="3"/>
@@ -7420,7 +7384,7 @@
         <v>367</v>
       </c>
       <c r="C361" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D361" s="5"/>
       <c r="E361" s="5"/>
@@ -7433,7 +7397,7 @@
         <v>368</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D362" s="3"/>
       <c r="E362" s="3"/>
@@ -7446,7 +7410,7 @@
         <v>369</v>
       </c>
       <c r="C363" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D363" s="5"/>
       <c r="E363" s="5"/>
@@ -7459,7 +7423,7 @@
         <v>370</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D364" s="3"/>
       <c r="E364" s="3"/>
@@ -7472,7 +7436,7 @@
         <v>371</v>
       </c>
       <c r="C365" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D365" s="5"/>
       <c r="E365" s="5"/>
@@ -7485,7 +7449,7 @@
         <v>372</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D366" s="3"/>
       <c r="E366" s="3"/>
@@ -7498,7 +7462,7 @@
         <v>373</v>
       </c>
       <c r="C367" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D367" s="5"/>
       <c r="E367" s="5"/>
@@ -7511,7 +7475,7 @@
         <v>374</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D368" s="3"/>
       <c r="E368" s="3"/>
@@ -7524,7 +7488,7 @@
         <v>375</v>
       </c>
       <c r="C369" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D369" s="5"/>
       <c r="E369" s="5"/>
@@ -7537,7 +7501,7 @@
         <v>376</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D370" s="3"/>
       <c r="E370" s="3"/>
@@ -7550,7 +7514,7 @@
         <v>377</v>
       </c>
       <c r="C371" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D371" s="5"/>
       <c r="E371" s="5"/>
@@ -7563,7 +7527,7 @@
         <v>378</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D372" s="3"/>
       <c r="E372" s="3"/>
@@ -7576,7 +7540,7 @@
         <v>379</v>
       </c>
       <c r="C373" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D373" s="5"/>
       <c r="E373" s="5"/>
@@ -7589,7 +7553,7 @@
         <v>380</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D374" s="3"/>
       <c r="E374" s="3"/>
@@ -7602,7 +7566,7 @@
         <v>381</v>
       </c>
       <c r="C375" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D375" s="5"/>
       <c r="E375" s="5"/>
@@ -7615,7 +7579,7 @@
         <v>382</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D376" s="3"/>
       <c r="E376" s="3"/>
@@ -7628,7 +7592,7 @@
         <v>383</v>
       </c>
       <c r="C377" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D377" s="5"/>
       <c r="E377" s="5"/>
@@ -7641,7 +7605,7 @@
         <v>384</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D378" s="3"/>
       <c r="E378" s="3"/>
@@ -7654,7 +7618,7 @@
         <v>385</v>
       </c>
       <c r="C379" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D379" s="5"/>
       <c r="E379" s="5"/>
@@ -7667,7 +7631,7 @@
         <v>386</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D380" s="3"/>
       <c r="E380" s="3"/>
@@ -7680,7 +7644,7 @@
         <v>387</v>
       </c>
       <c r="C381" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D381" s="5"/>
       <c r="E381" s="5"/>
@@ -7693,7 +7657,7 @@
         <v>388</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D382" s="3"/>
       <c r="E382" s="3"/>
@@ -7706,7 +7670,7 @@
         <v>389</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D383" s="5"/>
       <c r="E383" s="5"/>
@@ -7719,7 +7683,7 @@
         <v>390</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D384" s="3"/>
       <c r="E384" s="3"/>
@@ -7732,7 +7696,7 @@
         <v>391</v>
       </c>
       <c r="C385" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D385" s="5"/>
       <c r="E385" s="5"/>
@@ -7745,7 +7709,7 @@
         <v>392</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D386" s="3"/>
       <c r="E386" s="3"/>
@@ -7758,7 +7722,7 @@
         <v>393</v>
       </c>
       <c r="C387" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D387" s="5"/>
       <c r="E387" s="5"/>
@@ -7771,7 +7735,7 @@
         <v>394</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D388" s="3"/>
       <c r="E388" s="3"/>
@@ -7784,7 +7748,7 @@
         <v>395</v>
       </c>
       <c r="C389" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D389" s="5"/>
       <c r="E389" s="5"/>
@@ -7797,7 +7761,7 @@
         <v>396</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D390" s="3"/>
       <c r="E390" s="3"/>
@@ -7810,7 +7774,7 @@
         <v>397</v>
       </c>
       <c r="C391" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D391" s="5"/>
       <c r="E391" s="5"/>
@@ -7823,7 +7787,7 @@
         <v>398</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D392" s="3"/>
       <c r="E392" s="3"/>
@@ -7836,7 +7800,7 @@
         <v>399</v>
       </c>
       <c r="C393" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D393" s="5"/>
       <c r="E393" s="5"/>
@@ -7849,7 +7813,7 @@
         <v>400</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D394" s="3"/>
       <c r="E394" s="3"/>
@@ -7862,7 +7826,7 @@
         <v>401</v>
       </c>
       <c r="C395" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D395" s="5"/>
       <c r="E395" s="5"/>
@@ -7875,7 +7839,7 @@
         <v>402</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D396" s="3"/>
       <c r="E396" s="3"/>
@@ -7888,7 +7852,7 @@
         <v>403</v>
       </c>
       <c r="C397" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D397" s="5"/>
       <c r="E397" s="5"/>
@@ -7901,7 +7865,7 @@
         <v>404</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D398" s="3"/>
       <c r="E398" s="3"/>
@@ -7914,7 +7878,7 @@
         <v>405</v>
       </c>
       <c r="C399" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D399" s="5"/>
       <c r="E399" s="5"/>
@@ -7927,7 +7891,7 @@
         <v>406</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D400" s="3"/>
       <c r="E400" s="3"/>
@@ -7940,7 +7904,7 @@
         <v>407</v>
       </c>
       <c r="C401" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D401" s="5"/>
       <c r="E401" s="5"/>
@@ -7953,7 +7917,7 @@
         <v>408</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D402" s="3"/>
       <c r="E402" s="3"/>
@@ -7966,7 +7930,7 @@
         <v>409</v>
       </c>
       <c r="C403" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D403" s="5"/>
       <c r="E403" s="5"/>
@@ -7979,7 +7943,7 @@
         <v>410</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D404" s="3"/>
       <c r="E404" s="3"/>
@@ -7992,7 +7956,7 @@
         <v>411</v>
       </c>
       <c r="C405" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D405" s="5"/>
       <c r="E405" s="5"/>
@@ -8005,7 +7969,7 @@
         <v>412</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D406" s="3"/>
       <c r="E406" s="3"/>
@@ -8018,7 +7982,7 @@
         <v>413</v>
       </c>
       <c r="C407" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D407" s="5"/>
       <c r="E407" s="5"/>
@@ -8031,7 +7995,7 @@
         <v>414</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D408" s="3"/>
       <c r="E408" s="3"/>
@@ -8044,7 +8008,7 @@
         <v>415</v>
       </c>
       <c r="C409" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D409" s="5"/>
       <c r="E409" s="5"/>
@@ -8057,7 +8021,7 @@
         <v>416</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D410" s="3"/>
       <c r="E410" s="3"/>
@@ -8070,7 +8034,7 @@
         <v>417</v>
       </c>
       <c r="C411" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D411" s="5"/>
       <c r="E411" s="5"/>
@@ -8083,7 +8047,7 @@
         <v>418</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D412" s="3"/>
       <c r="E412" s="3"/>
@@ -8096,7 +8060,7 @@
         <v>419</v>
       </c>
       <c r="C413" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D413" s="5"/>
       <c r="E413" s="5"/>
@@ -8109,7 +8073,7 @@
         <v>420</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D414" s="3"/>
       <c r="E414" s="3"/>
@@ -8122,7 +8086,7 @@
         <v>421</v>
       </c>
       <c r="C415" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D415" s="5"/>
       <c r="E415" s="5"/>
@@ -8135,7 +8099,7 @@
         <v>422</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D416" s="3"/>
       <c r="E416" s="3"/>
@@ -8148,7 +8112,7 @@
         <v>423</v>
       </c>
       <c r="C417" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D417" s="5"/>
       <c r="E417" s="5"/>
@@ -8161,7 +8125,7 @@
         <v>424</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D418" s="3"/>
       <c r="E418" s="3"/>
@@ -8174,7 +8138,7 @@
         <v>425</v>
       </c>
       <c r="C419" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D419" s="5"/>
       <c r="E419" s="5"/>
@@ -8187,7 +8151,7 @@
         <v>426</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D420" s="3"/>
       <c r="E420" s="3"/>
@@ -8200,7 +8164,7 @@
         <v>427</v>
       </c>
       <c r="C421" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D421" s="5"/>
       <c r="E421" s="5"/>
@@ -8213,7 +8177,7 @@
         <v>428</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D422" s="3"/>
       <c r="E422" s="3"/>
@@ -8226,7 +8190,7 @@
         <v>429</v>
       </c>
       <c r="C423" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D423" s="5"/>
       <c r="E423" s="5"/>
@@ -8239,7 +8203,7 @@
         <v>430</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D424" s="3"/>
       <c r="E424" s="3"/>
@@ -8252,7 +8216,7 @@
         <v>431</v>
       </c>
       <c r="C425" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D425" s="5"/>
       <c r="E425" s="5"/>
@@ -8265,7 +8229,7 @@
         <v>432</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D426" s="3"/>
       <c r="E426" s="3"/>
@@ -8278,7 +8242,7 @@
         <v>433</v>
       </c>
       <c r="C427" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D427" s="5"/>
       <c r="E427" s="5"/>
@@ -8291,7 +8255,7 @@
         <v>434</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D428" s="3"/>
       <c r="E428" s="3"/>
@@ -8304,7 +8268,7 @@
         <v>435</v>
       </c>
       <c r="C429" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D429" s="5"/>
       <c r="E429" s="5"/>
@@ -8317,7 +8281,7 @@
         <v>436</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D430" s="3"/>
       <c r="E430" s="3"/>
@@ -8330,7 +8294,7 @@
         <v>437</v>
       </c>
       <c r="C431" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D431" s="5"/>
       <c r="E431" s="5"/>
@@ -8343,7 +8307,7 @@
         <v>438</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D432" s="3"/>
       <c r="E432" s="3"/>
@@ -8356,7 +8320,7 @@
         <v>439</v>
       </c>
       <c r="C433" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D433" s="5"/>
       <c r="E433" s="5"/>
@@ -8369,7 +8333,7 @@
         <v>440</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D434" s="3"/>
       <c r="E434" s="3"/>
@@ -8382,7 +8346,7 @@
         <v>441</v>
       </c>
       <c r="C435" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D435" s="5"/>
       <c r="E435" s="5"/>
@@ -8395,7 +8359,7 @@
         <v>442</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D436" s="3"/>
       <c r="E436" s="3"/>
@@ -8408,7 +8372,7 @@
         <v>443</v>
       </c>
       <c r="C437" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D437" s="5"/>
       <c r="E437" s="5"/>
@@ -8421,7 +8385,7 @@
         <v>444</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D438" s="3"/>
       <c r="E438" s="3"/>
@@ -8434,7 +8398,7 @@
         <v>445</v>
       </c>
       <c r="C439" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D439" s="5"/>
       <c r="E439" s="5"/>
@@ -8447,7 +8411,7 @@
         <v>446</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D440" s="3"/>
       <c r="E440" s="3"/>
@@ -8460,7 +8424,7 @@
         <v>447</v>
       </c>
       <c r="C441" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D441" s="5"/>
       <c r="E441" s="5"/>
@@ -8473,7 +8437,7 @@
         <v>448</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D442" s="3"/>
       <c r="E442" s="3"/>
@@ -8486,7 +8450,7 @@
         <v>449</v>
       </c>
       <c r="C443" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D443" s="5"/>
       <c r="E443" s="5"/>
@@ -8499,7 +8463,7 @@
         <v>450</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>288</v>
+        <v>451</v>
       </c>
       <c r="D444" s="3"/>
       <c r="E444" s="3"/>
@@ -8509,10 +8473,10 @@
         <v>444</v>
       </c>
       <c r="B445" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C445" s="6" t="s">
         <v>451</v>
-      </c>
-      <c r="C445" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="D445" s="5"/>
       <c r="E445" s="5"/>
@@ -8522,10 +8486,10 @@
         <v>445</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>288</v>
+        <v>451</v>
       </c>
       <c r="D446" s="3"/>
       <c r="E446" s="3"/>
@@ -8535,10 +8499,10 @@
         <v>446</v>
       </c>
       <c r="B447" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C447" s="6" t="s">
-        <v>288</v>
+        <v>451</v>
       </c>
       <c r="D447" s="5"/>
       <c r="E447" s="5"/>
@@ -8548,10 +8512,10 @@
         <v>447</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>288</v>
+        <v>451</v>
       </c>
       <c r="D448" s="3"/>
       <c r="E448" s="3"/>
@@ -8561,10 +8525,10 @@
         <v>448</v>
       </c>
       <c r="B449" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C449" s="6" t="s">
-        <v>288</v>
+        <v>451</v>
       </c>
       <c r="D449" s="5"/>
       <c r="E449" s="5"/>
@@ -8574,10 +8538,10 @@
         <v>449</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D450" s="3"/>
       <c r="E450" s="3"/>
@@ -8590,7 +8554,7 @@
         <v>458</v>
       </c>
       <c r="C451" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D451" s="5"/>
       <c r="E451" s="5"/>
@@ -8603,7 +8567,7 @@
         <v>459</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D452" s="3"/>
       <c r="E452" s="3"/>
@@ -8616,7 +8580,7 @@
         <v>460</v>
       </c>
       <c r="C453" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D453" s="5"/>
       <c r="E453" s="5"/>
@@ -8629,7 +8593,7 @@
         <v>461</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D454" s="3"/>
       <c r="E454" s="3"/>
@@ -8642,7 +8606,7 @@
         <v>462</v>
       </c>
       <c r="C455" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D455" s="5"/>
       <c r="E455" s="5"/>
@@ -8655,7 +8619,7 @@
         <v>463</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D456" s="3"/>
       <c r="E456" s="3"/>
@@ -8668,7 +8632,7 @@
         <v>464</v>
       </c>
       <c r="C457" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D457" s="5"/>
       <c r="E457" s="5"/>
@@ -8681,7 +8645,7 @@
         <v>465</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D458" s="3"/>
       <c r="E458" s="3"/>
@@ -8694,7 +8658,7 @@
         <v>466</v>
       </c>
       <c r="C459" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D459" s="5"/>
       <c r="E459" s="5"/>
@@ -8707,7 +8671,7 @@
         <v>467</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D460" s="3"/>
       <c r="E460" s="3"/>
@@ -8720,7 +8684,7 @@
         <v>468</v>
       </c>
       <c r="C461" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D461" s="5"/>
       <c r="E461" s="5"/>
@@ -8733,7 +8697,7 @@
         <v>469</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D462" s="3"/>
       <c r="E462" s="3"/>
@@ -8746,7 +8710,7 @@
         <v>470</v>
       </c>
       <c r="C463" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D463" s="5"/>
       <c r="E463" s="5"/>
@@ -8759,7 +8723,7 @@
         <v>471</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D464" s="3"/>
       <c r="E464" s="3"/>
@@ -8772,7 +8736,7 @@
         <v>472</v>
       </c>
       <c r="C465" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D465" s="5"/>
       <c r="E465" s="5"/>
@@ -8785,7 +8749,7 @@
         <v>473</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D466" s="3"/>
       <c r="E466" s="3"/>
@@ -8798,7 +8762,7 @@
         <v>474</v>
       </c>
       <c r="C467" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D467" s="5"/>
       <c r="E467" s="5"/>
@@ -8811,7 +8775,7 @@
         <v>475</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D468" s="3"/>
       <c r="E468" s="3"/>
@@ -8824,7 +8788,7 @@
         <v>476</v>
       </c>
       <c r="C469" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D469" s="5"/>
       <c r="E469" s="5"/>
@@ -8837,7 +8801,7 @@
         <v>477</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D470" s="3"/>
       <c r="E470" s="3"/>
@@ -8850,7 +8814,7 @@
         <v>478</v>
       </c>
       <c r="C471" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D471" s="5"/>
       <c r="E471" s="5"/>
@@ -8863,7 +8827,7 @@
         <v>479</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D472" s="3"/>
       <c r="E472" s="3"/>
@@ -8876,7 +8840,7 @@
         <v>480</v>
       </c>
       <c r="C473" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D473" s="5"/>
       <c r="E473" s="5"/>
@@ -8889,7 +8853,7 @@
         <v>481</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D474" s="3"/>
       <c r="E474" s="3"/>
@@ -8902,7 +8866,7 @@
         <v>482</v>
       </c>
       <c r="C475" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D475" s="5"/>
       <c r="E475" s="5"/>
@@ -8915,7 +8879,7 @@
         <v>483</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D476" s="3"/>
       <c r="E476" s="3"/>
@@ -8928,7 +8892,7 @@
         <v>484</v>
       </c>
       <c r="C477" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D477" s="5"/>
       <c r="E477" s="5"/>
@@ -8941,7 +8905,7 @@
         <v>485</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D478" s="3"/>
       <c r="E478" s="3"/>
@@ -8954,7 +8918,7 @@
         <v>486</v>
       </c>
       <c r="C479" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D479" s="5"/>
       <c r="E479" s="5"/>
@@ -8967,7 +8931,7 @@
         <v>487</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D480" s="3"/>
       <c r="E480" s="3"/>
@@ -8980,7 +8944,7 @@
         <v>488</v>
       </c>
       <c r="C481" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D481" s="5"/>
       <c r="E481" s="5"/>
@@ -8993,7 +8957,7 @@
         <v>489</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D482" s="3"/>
       <c r="E482" s="3"/>
@@ -9006,7 +8970,7 @@
         <v>490</v>
       </c>
       <c r="C483" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D483" s="5"/>
       <c r="E483" s="5"/>
@@ -9019,7 +8983,7 @@
         <v>491</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D484" s="3"/>
       <c r="E484" s="3"/>
@@ -9032,7 +8996,7 @@
         <v>492</v>
       </c>
       <c r="C485" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D485" s="5"/>
       <c r="E485" s="5"/>
@@ -9045,7 +9009,7 @@
         <v>493</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D486" s="3"/>
       <c r="E486" s="3"/>
@@ -9058,7 +9022,7 @@
         <v>494</v>
       </c>
       <c r="C487" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D487" s="5"/>
       <c r="E487" s="5"/>
@@ -9071,7 +9035,7 @@
         <v>495</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D488" s="3"/>
       <c r="E488" s="3"/>
@@ -9084,7 +9048,7 @@
         <v>496</v>
       </c>
       <c r="C489" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D489" s="5"/>
       <c r="E489" s="5"/>
@@ -9097,7 +9061,7 @@
         <v>497</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D490" s="3"/>
       <c r="E490" s="3"/>
@@ -9110,7 +9074,7 @@
         <v>498</v>
       </c>
       <c r="C491" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D491" s="5"/>
       <c r="E491" s="5"/>
@@ -9123,7 +9087,7 @@
         <v>499</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D492" s="3"/>
       <c r="E492" s="3"/>
@@ -9136,7 +9100,7 @@
         <v>500</v>
       </c>
       <c r="C493" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D493" s="5"/>
       <c r="E493" s="5"/>
@@ -9149,7 +9113,7 @@
         <v>501</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D494" s="3"/>
       <c r="E494" s="3"/>
@@ -9162,7 +9126,7 @@
         <v>502</v>
       </c>
       <c r="C495" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D495" s="5"/>
       <c r="E495" s="5"/>
@@ -9175,7 +9139,7 @@
         <v>503</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D496" s="3"/>
       <c r="E496" s="3"/>
@@ -9188,7 +9152,7 @@
         <v>504</v>
       </c>
       <c r="C497" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D497" s="5"/>
       <c r="E497" s="5"/>
@@ -9201,7 +9165,7 @@
         <v>505</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D498" s="3"/>
       <c r="E498" s="3"/>
@@ -9214,7 +9178,7 @@
         <v>506</v>
       </c>
       <c r="C499" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D499" s="5"/>
       <c r="E499" s="5"/>
@@ -9227,7 +9191,7 @@
         <v>507</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D500" s="3"/>
       <c r="E500" s="3"/>
@@ -9240,7 +9204,7 @@
         <v>508</v>
       </c>
       <c r="C501" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D501" s="5"/>
       <c r="E501" s="5"/>
@@ -9253,7 +9217,7 @@
         <v>509</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D502" s="3"/>
       <c r="E502" s="3"/>
@@ -9266,7 +9230,7 @@
         <v>510</v>
       </c>
       <c r="C503" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D503" s="5"/>
       <c r="E503" s="5"/>
@@ -9279,7 +9243,7 @@
         <v>511</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D504" s="3"/>
       <c r="E504" s="3"/>
@@ -9292,7 +9256,7 @@
         <v>512</v>
       </c>
       <c r="C505" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D505" s="5"/>
       <c r="E505" s="5"/>
@@ -9305,7 +9269,7 @@
         <v>513</v>
       </c>
       <c r="C506" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D506" s="3"/>
       <c r="E506" s="3"/>
@@ -9318,7 +9282,7 @@
         <v>514</v>
       </c>
       <c r="C507" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D507" s="5"/>
       <c r="E507" s="5"/>
@@ -9331,7 +9295,7 @@
         <v>515</v>
       </c>
       <c r="C508" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D508" s="3"/>
       <c r="E508" s="3"/>
@@ -9344,7 +9308,7 @@
         <v>516</v>
       </c>
       <c r="C509" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D509" s="5"/>
       <c r="E509" s="5"/>
@@ -9357,7 +9321,7 @@
         <v>517</v>
       </c>
       <c r="C510" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D510" s="3"/>
       <c r="E510" s="3"/>
@@ -9370,7 +9334,7 @@
         <v>518</v>
       </c>
       <c r="C511" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D511" s="5"/>
       <c r="E511" s="5"/>
@@ -9383,7 +9347,7 @@
         <v>519</v>
       </c>
       <c r="C512" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D512" s="3"/>
       <c r="E512" s="3"/>
@@ -9396,7 +9360,7 @@
         <v>520</v>
       </c>
       <c r="C513" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D513" s="5"/>
       <c r="E513" s="5"/>
@@ -9409,7 +9373,7 @@
         <v>521</v>
       </c>
       <c r="C514" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D514" s="3"/>
       <c r="E514" s="3"/>
@@ -9422,7 +9386,7 @@
         <v>522</v>
       </c>
       <c r="C515" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D515" s="5"/>
       <c r="E515" s="5"/>
@@ -9435,7 +9399,7 @@
         <v>523</v>
       </c>
       <c r="C516" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D516" s="3"/>
       <c r="E516" s="3"/>
@@ -9448,7 +9412,7 @@
         <v>524</v>
       </c>
       <c r="C517" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D517" s="5"/>
       <c r="E517" s="5"/>
@@ -9461,7 +9425,7 @@
         <v>525</v>
       </c>
       <c r="C518" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D518" s="3"/>
       <c r="E518" s="3"/>
@@ -9474,7 +9438,7 @@
         <v>526</v>
       </c>
       <c r="C519" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D519" s="5"/>
       <c r="E519" s="5"/>
@@ -9487,7 +9451,7 @@
         <v>527</v>
       </c>
       <c r="C520" s="4" t="s">
-        <v>457</v>
+        <v>528</v>
       </c>
       <c r="D520" s="3"/>
       <c r="E520" s="3"/>
@@ -9497,10 +9461,10 @@
         <v>520</v>
       </c>
       <c r="B521" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="C521" s="6" t="s">
         <v>528</v>
-      </c>
-      <c r="C521" s="6" t="s">
-        <v>457</v>
       </c>
       <c r="D521" s="5"/>
       <c r="E521" s="5"/>
@@ -9510,10 +9474,10 @@
         <v>521</v>
       </c>
       <c r="B522" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C522" s="4" t="s">
-        <v>457</v>
+        <v>528</v>
       </c>
       <c r="D522" s="3"/>
       <c r="E522" s="3"/>
@@ -9523,10 +9487,10 @@
         <v>522</v>
       </c>
       <c r="B523" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C523" s="6" t="s">
-        <v>457</v>
+        <v>528</v>
       </c>
       <c r="D523" s="5"/>
       <c r="E523" s="5"/>
@@ -9536,10 +9500,10 @@
         <v>523</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C524" s="4" t="s">
-        <v>457</v>
+        <v>528</v>
       </c>
       <c r="D524" s="3"/>
       <c r="E524" s="3"/>
@@ -9549,10 +9513,10 @@
         <v>524</v>
       </c>
       <c r="B525" s="5" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C525" s="6" t="s">
-        <v>457</v>
+        <v>528</v>
       </c>
       <c r="D525" s="5"/>
       <c r="E525" s="5"/>
@@ -9562,10 +9526,10 @@
         <v>525</v>
       </c>
       <c r="B526" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C526" s="4" t="s">
-        <v>457</v>
+        <v>528</v>
       </c>
       <c r="D526" s="3"/>
       <c r="E526" s="3"/>
@@ -9575,10 +9539,10 @@
         <v>526</v>
       </c>
       <c r="B527" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C527" s="6" t="s">
-        <v>457</v>
+        <v>528</v>
       </c>
       <c r="D527" s="5"/>
       <c r="E527" s="5"/>
@@ -9588,10 +9552,10 @@
         <v>527</v>
       </c>
       <c r="B528" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C528" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D528" s="3"/>
       <c r="E528" s="3"/>
@@ -9604,7 +9568,7 @@
         <v>537</v>
       </c>
       <c r="C529" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D529" s="5"/>
       <c r="E529" s="5"/>
@@ -9617,7 +9581,7 @@
         <v>538</v>
       </c>
       <c r="C530" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D530" s="3"/>
       <c r="E530" s="3"/>
@@ -9630,7 +9594,7 @@
         <v>539</v>
       </c>
       <c r="C531" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D531" s="5"/>
       <c r="E531" s="5"/>
@@ -9643,7 +9607,7 @@
         <v>540</v>
       </c>
       <c r="C532" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D532" s="3"/>
       <c r="E532" s="3"/>
@@ -9656,7 +9620,7 @@
         <v>541</v>
       </c>
       <c r="C533" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D533" s="5"/>
       <c r="E533" s="5"/>
@@ -9669,7 +9633,7 @@
         <v>542</v>
       </c>
       <c r="C534" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D534" s="3"/>
       <c r="E534" s="3"/>
@@ -9682,7 +9646,7 @@
         <v>543</v>
       </c>
       <c r="C535" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D535" s="5"/>
       <c r="E535" s="5"/>
@@ -9695,7 +9659,7 @@
         <v>544</v>
       </c>
       <c r="C536" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D536" s="3"/>
       <c r="E536" s="3"/>
@@ -9708,7 +9672,7 @@
         <v>545</v>
       </c>
       <c r="C537" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D537" s="5"/>
       <c r="E537" s="5"/>
@@ -9721,7 +9685,7 @@
         <v>546</v>
       </c>
       <c r="C538" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D538" s="3"/>
       <c r="E538" s="3"/>
@@ -9734,7 +9698,7 @@
         <v>547</v>
       </c>
       <c r="C539" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D539" s="5"/>
       <c r="E539" s="5"/>
@@ -9747,7 +9711,7 @@
         <v>548</v>
       </c>
       <c r="C540" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D540" s="3"/>
       <c r="E540" s="3"/>
@@ -9760,7 +9724,7 @@
         <v>549</v>
       </c>
       <c r="C541" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D541" s="5"/>
       <c r="E541" s="5"/>
@@ -9773,7 +9737,7 @@
         <v>550</v>
       </c>
       <c r="C542" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D542" s="3"/>
       <c r="E542" s="3"/>
@@ -9786,7 +9750,7 @@
         <v>551</v>
       </c>
       <c r="C543" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D543" s="5"/>
       <c r="E543" s="5"/>
@@ -9799,7 +9763,7 @@
         <v>552</v>
       </c>
       <c r="C544" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D544" s="3"/>
       <c r="E544" s="3"/>
@@ -9812,7 +9776,7 @@
         <v>553</v>
       </c>
       <c r="C545" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D545" s="5"/>
       <c r="E545" s="5"/>
@@ -9825,7 +9789,7 @@
         <v>554</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D546" s="3"/>
       <c r="E546" s="3"/>
@@ -9838,7 +9802,7 @@
         <v>555</v>
       </c>
       <c r="C547" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D547" s="5"/>
       <c r="E547" s="5"/>
@@ -9851,7 +9815,7 @@
         <v>556</v>
       </c>
       <c r="C548" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D548" s="3"/>
       <c r="E548" s="3"/>
@@ -9864,7 +9828,7 @@
         <v>557</v>
       </c>
       <c r="C549" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D549" s="5"/>
       <c r="E549" s="5"/>
@@ -9877,7 +9841,7 @@
         <v>558</v>
       </c>
       <c r="C550" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D550" s="3"/>
       <c r="E550" s="3"/>
@@ -9890,7 +9854,7 @@
         <v>559</v>
       </c>
       <c r="C551" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D551" s="5"/>
       <c r="E551" s="5"/>
@@ -9903,7 +9867,7 @@
         <v>560</v>
       </c>
       <c r="C552" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D552" s="3"/>
       <c r="E552" s="3"/>
@@ -9916,7 +9880,7 @@
         <v>561</v>
       </c>
       <c r="C553" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D553" s="5"/>
       <c r="E553" s="5"/>
@@ -9929,7 +9893,7 @@
         <v>562</v>
       </c>
       <c r="C554" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D554" s="3"/>
       <c r="E554" s="3"/>
@@ -9942,7 +9906,7 @@
         <v>563</v>
       </c>
       <c r="C555" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D555" s="5"/>
       <c r="E555" s="5"/>
@@ -9955,7 +9919,7 @@
         <v>564</v>
       </c>
       <c r="C556" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D556" s="3"/>
       <c r="E556" s="3"/>
@@ -9968,7 +9932,7 @@
         <v>565</v>
       </c>
       <c r="C557" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D557" s="5"/>
       <c r="E557" s="5"/>
@@ -9981,7 +9945,7 @@
         <v>566</v>
       </c>
       <c r="C558" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D558" s="3"/>
       <c r="E558" s="3"/>
@@ -9994,7 +9958,7 @@
         <v>567</v>
       </c>
       <c r="C559" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D559" s="5"/>
       <c r="E559" s="5"/>
@@ -10007,7 +9971,7 @@
         <v>568</v>
       </c>
       <c r="C560" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D560" s="3"/>
       <c r="E560" s="3"/>
@@ -10020,7 +9984,7 @@
         <v>569</v>
       </c>
       <c r="C561" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D561" s="5"/>
       <c r="E561" s="5"/>
@@ -10033,7 +9997,7 @@
         <v>570</v>
       </c>
       <c r="C562" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D562" s="3"/>
       <c r="E562" s="3"/>
@@ -10046,7 +10010,7 @@
         <v>571</v>
       </c>
       <c r="C563" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D563" s="5"/>
       <c r="E563" s="5"/>
@@ -10059,7 +10023,7 @@
         <v>572</v>
       </c>
       <c r="C564" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D564" s="3"/>
       <c r="E564" s="3"/>
@@ -10072,7 +10036,7 @@
         <v>573</v>
       </c>
       <c r="C565" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D565" s="5"/>
       <c r="E565" s="5"/>
@@ -10085,7 +10049,7 @@
         <v>574</v>
       </c>
       <c r="C566" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D566" s="3"/>
       <c r="E566" s="3"/>
@@ -10098,7 +10062,7 @@
         <v>575</v>
       </c>
       <c r="C567" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D567" s="5"/>
       <c r="E567" s="5"/>
@@ -10111,7 +10075,7 @@
         <v>576</v>
       </c>
       <c r="C568" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D568" s="3"/>
       <c r="E568" s="3"/>
@@ -10124,7 +10088,7 @@
         <v>577</v>
       </c>
       <c r="C569" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D569" s="5"/>
       <c r="E569" s="5"/>
@@ -10137,7 +10101,7 @@
         <v>578</v>
       </c>
       <c r="C570" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D570" s="3"/>
       <c r="E570" s="3"/>
@@ -10150,7 +10114,7 @@
         <v>579</v>
       </c>
       <c r="C571" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D571" s="5"/>
       <c r="E571" s="5"/>
@@ -10163,7 +10127,7 @@
         <v>580</v>
       </c>
       <c r="C572" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D572" s="3"/>
       <c r="E572" s="3"/>
@@ -10176,7 +10140,7 @@
         <v>581</v>
       </c>
       <c r="C573" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D573" s="5"/>
       <c r="E573" s="5"/>
@@ -10189,7 +10153,7 @@
         <v>582</v>
       </c>
       <c r="C574" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D574" s="3"/>
       <c r="E574" s="3"/>
@@ -10202,7 +10166,7 @@
         <v>583</v>
       </c>
       <c r="C575" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D575" s="5"/>
       <c r="E575" s="5"/>
@@ -10215,7 +10179,7 @@
         <v>584</v>
       </c>
       <c r="C576" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D576" s="3"/>
       <c r="E576" s="3"/>
@@ -10228,7 +10192,7 @@
         <v>585</v>
       </c>
       <c r="C577" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D577" s="5"/>
       <c r="E577" s="5"/>
@@ -10241,7 +10205,7 @@
         <v>586</v>
       </c>
       <c r="C578" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D578" s="3"/>
       <c r="E578" s="3"/>
@@ -10254,7 +10218,7 @@
         <v>587</v>
       </c>
       <c r="C579" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D579" s="5"/>
       <c r="E579" s="5"/>
@@ -10267,7 +10231,7 @@
         <v>588</v>
       </c>
       <c r="C580" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D580" s="3"/>
       <c r="E580" s="3"/>
@@ -10280,7 +10244,7 @@
         <v>589</v>
       </c>
       <c r="C581" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D581" s="5"/>
       <c r="E581" s="5"/>
@@ -10293,7 +10257,7 @@
         <v>590</v>
       </c>
       <c r="C582" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D582" s="3"/>
       <c r="E582" s="3"/>
@@ -10306,7 +10270,7 @@
         <v>591</v>
       </c>
       <c r="C583" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D583" s="5"/>
       <c r="E583" s="5"/>
@@ -10319,7 +10283,7 @@
         <v>592</v>
       </c>
       <c r="C584" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D584" s="3"/>
       <c r="E584" s="3"/>
@@ -10332,7 +10296,7 @@
         <v>593</v>
       </c>
       <c r="C585" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D585" s="5"/>
       <c r="E585" s="5"/>
@@ -10345,7 +10309,7 @@
         <v>594</v>
       </c>
       <c r="C586" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D586" s="3"/>
       <c r="E586" s="3"/>
@@ -10358,7 +10322,7 @@
         <v>595</v>
       </c>
       <c r="C587" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D587" s="5"/>
       <c r="E587" s="5"/>
@@ -10371,7 +10335,7 @@
         <v>596</v>
       </c>
       <c r="C588" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D588" s="3"/>
       <c r="E588" s="3"/>
@@ -10384,7 +10348,7 @@
         <v>597</v>
       </c>
       <c r="C589" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D589" s="5"/>
       <c r="E589" s="5"/>
@@ -10397,7 +10361,7 @@
         <v>598</v>
       </c>
       <c r="C590" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D590" s="3"/>
       <c r="E590" s="3"/>
@@ -10410,7 +10374,7 @@
         <v>599</v>
       </c>
       <c r="C591" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D591" s="5"/>
       <c r="E591" s="5"/>
@@ -10423,7 +10387,7 @@
         <v>600</v>
       </c>
       <c r="C592" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D592" s="3"/>
       <c r="E592" s="3"/>
@@ -10436,7 +10400,7 @@
         <v>601</v>
       </c>
       <c r="C593" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D593" s="5"/>
       <c r="E593" s="5"/>
@@ -10449,7 +10413,7 @@
         <v>602</v>
       </c>
       <c r="C594" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D594" s="3"/>
       <c r="E594" s="3"/>
@@ -10462,7 +10426,7 @@
         <v>603</v>
       </c>
       <c r="C595" s="6" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D595" s="5"/>
       <c r="E595" s="5"/>
@@ -10475,7 +10439,7 @@
         <v>604</v>
       </c>
       <c r="C596" s="4" t="s">
-        <v>536</v>
+        <v>605</v>
       </c>
       <c r="D596" s="3"/>
       <c r="E596" s="3"/>
@@ -10485,10 +10449,10 @@
         <v>596</v>
       </c>
       <c r="B597" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="C597" s="6" t="s">
         <v>605</v>
-      </c>
-      <c r="C597" s="6" t="s">
-        <v>536</v>
       </c>
       <c r="D597" s="5"/>
       <c r="E597" s="5"/>
@@ -10498,10 +10462,10 @@
         <v>597</v>
       </c>
       <c r="B598" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C598" s="4" t="s">
-        <v>536</v>
+        <v>605</v>
       </c>
       <c r="D598" s="3"/>
       <c r="E598" s="3"/>
@@ -10511,10 +10475,10 @@
         <v>598</v>
       </c>
       <c r="B599" s="5" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C599" s="6" t="s">
-        <v>536</v>
+        <v>605</v>
       </c>
       <c r="D599" s="5"/>
       <c r="E599" s="5"/>
@@ -10524,10 +10488,10 @@
         <v>599</v>
       </c>
       <c r="B600" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C600" s="4" t="s">
-        <v>536</v>
+        <v>605</v>
       </c>
       <c r="D600" s="3"/>
       <c r="E600" s="3"/>
@@ -10537,10 +10501,10 @@
         <v>600</v>
       </c>
       <c r="B601" s="5" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C601" s="6" t="s">
-        <v>536</v>
+        <v>605</v>
       </c>
       <c r="D601" s="5"/>
       <c r="E601" s="5"/>
@@ -10550,10 +10514,10 @@
         <v>601</v>
       </c>
       <c r="B602" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C602" s="4" t="s">
-        <v>536</v>
+        <v>605</v>
       </c>
       <c r="D602" s="3"/>
       <c r="E602" s="3"/>
@@ -10563,10 +10527,10 @@
         <v>602</v>
       </c>
       <c r="B603" s="5" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C603" s="6" t="s">
-        <v>536</v>
+        <v>605</v>
       </c>
       <c r="D603" s="5"/>
       <c r="E603" s="5"/>
@@ -10576,10 +10540,10 @@
         <v>603</v>
       </c>
       <c r="B604" s="3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C604" s="4" t="s">
-        <v>536</v>
+        <v>605</v>
       </c>
       <c r="D604" s="3"/>
       <c r="E604" s="3"/>
@@ -10589,10 +10553,10 @@
         <v>604</v>
       </c>
       <c r="B605" s="5" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C605" s="6" t="s">
-        <v>536</v>
+        <v>605</v>
       </c>
       <c r="D605" s="5"/>
       <c r="E605" s="5"/>
@@ -10602,10 +10566,10 @@
         <v>605</v>
       </c>
       <c r="B606" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C606" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D606" s="3"/>
       <c r="E606" s="3"/>
@@ -10618,7 +10582,7 @@
         <v>616</v>
       </c>
       <c r="C607" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D607" s="5"/>
       <c r="E607" s="5"/>
@@ -10631,7 +10595,7 @@
         <v>617</v>
       </c>
       <c r="C608" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D608" s="3"/>
       <c r="E608" s="3"/>
@@ -10644,7 +10608,7 @@
         <v>618</v>
       </c>
       <c r="C609" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D609" s="5"/>
       <c r="E609" s="5"/>
@@ -10657,7 +10621,7 @@
         <v>619</v>
       </c>
       <c r="C610" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D610" s="3"/>
       <c r="E610" s="3"/>
@@ -10670,7 +10634,7 @@
         <v>620</v>
       </c>
       <c r="C611" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D611" s="5"/>
       <c r="E611" s="5"/>
@@ -10683,7 +10647,7 @@
         <v>621</v>
       </c>
       <c r="C612" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D612" s="3"/>
       <c r="E612" s="3"/>
@@ -10696,7 +10660,7 @@
         <v>622</v>
       </c>
       <c r="C613" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D613" s="5"/>
       <c r="E613" s="5"/>
@@ -10709,7 +10673,7 @@
         <v>623</v>
       </c>
       <c r="C614" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D614" s="3"/>
       <c r="E614" s="3"/>
@@ -10722,7 +10686,7 @@
         <v>624</v>
       </c>
       <c r="C615" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D615" s="5"/>
       <c r="E615" s="5"/>
@@ -10735,7 +10699,7 @@
         <v>625</v>
       </c>
       <c r="C616" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D616" s="3"/>
       <c r="E616" s="3"/>
@@ -10748,7 +10712,7 @@
         <v>626</v>
       </c>
       <c r="C617" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D617" s="5"/>
       <c r="E617" s="5"/>
@@ -10761,7 +10725,7 @@
         <v>627</v>
       </c>
       <c r="C618" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D618" s="3"/>
       <c r="E618" s="3"/>
@@ -10774,7 +10738,7 @@
         <v>628</v>
       </c>
       <c r="C619" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D619" s="5"/>
       <c r="E619" s="5"/>
@@ -10787,7 +10751,7 @@
         <v>629</v>
       </c>
       <c r="C620" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D620" s="3"/>
       <c r="E620" s="3"/>
@@ -10800,7 +10764,7 @@
         <v>630</v>
       </c>
       <c r="C621" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D621" s="5"/>
       <c r="E621" s="5"/>
@@ -10813,7 +10777,7 @@
         <v>631</v>
       </c>
       <c r="C622" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D622" s="3"/>
       <c r="E622" s="3"/>
@@ -10826,7 +10790,7 @@
         <v>632</v>
       </c>
       <c r="C623" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D623" s="5"/>
       <c r="E623" s="5"/>
@@ -10839,7 +10803,7 @@
         <v>633</v>
       </c>
       <c r="C624" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D624" s="3"/>
       <c r="E624" s="3"/>
@@ -10852,7 +10816,7 @@
         <v>634</v>
       </c>
       <c r="C625" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D625" s="5"/>
       <c r="E625" s="5"/>
@@ -10865,7 +10829,7 @@
         <v>635</v>
       </c>
       <c r="C626" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D626" s="3"/>
       <c r="E626" s="3"/>
@@ -10878,7 +10842,7 @@
         <v>636</v>
       </c>
       <c r="C627" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D627" s="5"/>
       <c r="E627" s="5"/>
@@ -10891,7 +10855,7 @@
         <v>637</v>
       </c>
       <c r="C628" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D628" s="3"/>
       <c r="E628" s="3"/>
@@ -10904,7 +10868,7 @@
         <v>638</v>
       </c>
       <c r="C629" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D629" s="5"/>
       <c r="E629" s="5"/>
@@ -10917,7 +10881,7 @@
         <v>639</v>
       </c>
       <c r="C630" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D630" s="3"/>
       <c r="E630" s="3"/>
@@ -10930,7 +10894,7 @@
         <v>640</v>
       </c>
       <c r="C631" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D631" s="5"/>
       <c r="E631" s="5"/>
@@ -10943,7 +10907,7 @@
         <v>641</v>
       </c>
       <c r="C632" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D632" s="3"/>
       <c r="E632" s="3"/>
@@ -10956,7 +10920,7 @@
         <v>642</v>
       </c>
       <c r="C633" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D633" s="5"/>
       <c r="E633" s="5"/>
@@ -10969,7 +10933,7 @@
         <v>643</v>
       </c>
       <c r="C634" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D634" s="3"/>
       <c r="E634" s="3"/>
@@ -10982,7 +10946,7 @@
         <v>644</v>
       </c>
       <c r="C635" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D635" s="5"/>
       <c r="E635" s="5"/>
@@ -10995,7 +10959,7 @@
         <v>645</v>
       </c>
       <c r="C636" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D636" s="3"/>
       <c r="E636" s="3"/>
@@ -11008,7 +10972,7 @@
         <v>646</v>
       </c>
       <c r="C637" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D637" s="5"/>
       <c r="E637" s="5"/>
@@ -11021,7 +10985,7 @@
         <v>647</v>
       </c>
       <c r="C638" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D638" s="3"/>
       <c r="E638" s="3"/>
@@ -11034,7 +10998,7 @@
         <v>648</v>
       </c>
       <c r="C639" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D639" s="5"/>
       <c r="E639" s="5"/>
@@ -11047,7 +11011,7 @@
         <v>649</v>
       </c>
       <c r="C640" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D640" s="3"/>
       <c r="E640" s="3"/>
@@ -11060,7 +11024,7 @@
         <v>650</v>
       </c>
       <c r="C641" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D641" s="5"/>
       <c r="E641" s="5"/>
@@ -11073,7 +11037,7 @@
         <v>651</v>
       </c>
       <c r="C642" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D642" s="3"/>
       <c r="E642" s="3"/>
@@ -11086,7 +11050,7 @@
         <v>652</v>
       </c>
       <c r="C643" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D643" s="5"/>
       <c r="E643" s="5"/>
@@ -11099,7 +11063,7 @@
         <v>653</v>
       </c>
       <c r="C644" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D644" s="3"/>
       <c r="E644" s="3"/>
@@ -11112,7 +11076,7 @@
         <v>654</v>
       </c>
       <c r="C645" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D645" s="5"/>
       <c r="E645" s="5"/>
@@ -11125,7 +11089,7 @@
         <v>655</v>
       </c>
       <c r="C646" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D646" s="3"/>
       <c r="E646" s="3"/>
@@ -11138,7 +11102,7 @@
         <v>656</v>
       </c>
       <c r="C647" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D647" s="5"/>
       <c r="E647" s="5"/>
@@ -11151,7 +11115,7 @@
         <v>657</v>
       </c>
       <c r="C648" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D648" s="3"/>
       <c r="E648" s="3"/>
@@ -11164,7 +11128,7 @@
         <v>658</v>
       </c>
       <c r="C649" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D649" s="5"/>
       <c r="E649" s="5"/>
@@ -11177,7 +11141,7 @@
         <v>659</v>
       </c>
       <c r="C650" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D650" s="3"/>
       <c r="E650" s="3"/>
@@ -11190,7 +11154,7 @@
         <v>660</v>
       </c>
       <c r="C651" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D651" s="5"/>
       <c r="E651" s="5"/>
@@ -11203,7 +11167,7 @@
         <v>661</v>
       </c>
       <c r="C652" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D652" s="3"/>
       <c r="E652" s="3"/>
@@ -11216,7 +11180,7 @@
         <v>662</v>
       </c>
       <c r="C653" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D653" s="5"/>
       <c r="E653" s="5"/>
@@ -11229,7 +11193,7 @@
         <v>663</v>
       </c>
       <c r="C654" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D654" s="3"/>
       <c r="E654" s="3"/>
@@ -11242,7 +11206,7 @@
         <v>664</v>
       </c>
       <c r="C655" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D655" s="5"/>
       <c r="E655" s="5"/>
@@ -11255,7 +11219,7 @@
         <v>665</v>
       </c>
       <c r="C656" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D656" s="3"/>
       <c r="E656" s="3"/>
@@ -11268,7 +11232,7 @@
         <v>666</v>
       </c>
       <c r="C657" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D657" s="5"/>
       <c r="E657" s="5"/>
@@ -11281,7 +11245,7 @@
         <v>667</v>
       </c>
       <c r="C658" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D658" s="3"/>
       <c r="E658" s="3"/>
@@ -11294,7 +11258,7 @@
         <v>668</v>
       </c>
       <c r="C659" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D659" s="5"/>
       <c r="E659" s="5"/>
@@ -11307,7 +11271,7 @@
         <v>669</v>
       </c>
       <c r="C660" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D660" s="3"/>
       <c r="E660" s="3"/>
@@ -11320,7 +11284,7 @@
         <v>670</v>
       </c>
       <c r="C661" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D661" s="5"/>
       <c r="E661" s="5"/>
@@ -11333,7 +11297,7 @@
         <v>671</v>
       </c>
       <c r="C662" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D662" s="3"/>
       <c r="E662" s="3"/>
@@ -11346,7 +11310,7 @@
         <v>672</v>
       </c>
       <c r="C663" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D663" s="5"/>
       <c r="E663" s="5"/>
@@ -11359,7 +11323,7 @@
         <v>673</v>
       </c>
       <c r="C664" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D664" s="3"/>
       <c r="E664" s="3"/>
@@ -11372,7 +11336,7 @@
         <v>674</v>
       </c>
       <c r="C665" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D665" s="5"/>
       <c r="E665" s="5"/>
@@ -11385,7 +11349,7 @@
         <v>675</v>
       </c>
       <c r="C666" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D666" s="3"/>
       <c r="E666" s="3"/>
@@ -11398,7 +11362,7 @@
         <v>676</v>
       </c>
       <c r="C667" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D667" s="5"/>
       <c r="E667" s="5"/>
@@ -11411,7 +11375,7 @@
         <v>677</v>
       </c>
       <c r="C668" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D668" s="3"/>
       <c r="E668" s="3"/>
@@ -11424,7 +11388,7 @@
         <v>678</v>
       </c>
       <c r="C669" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D669" s="5"/>
       <c r="E669" s="5"/>
@@ -11437,7 +11401,7 @@
         <v>679</v>
       </c>
       <c r="C670" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D670" s="3"/>
       <c r="E670" s="3"/>
@@ -11450,7 +11414,7 @@
         <v>680</v>
       </c>
       <c r="C671" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D671" s="5"/>
       <c r="E671" s="5"/>
@@ -11463,7 +11427,7 @@
         <v>681</v>
       </c>
       <c r="C672" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D672" s="3"/>
       <c r="E672" s="3"/>
@@ -11476,7 +11440,7 @@
         <v>682</v>
       </c>
       <c r="C673" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D673" s="5"/>
       <c r="E673" s="5"/>
@@ -11489,7 +11453,7 @@
         <v>683</v>
       </c>
       <c r="C674" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D674" s="3"/>
       <c r="E674" s="3"/>
@@ -11502,7 +11466,7 @@
         <v>684</v>
       </c>
       <c r="C675" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D675" s="5"/>
       <c r="E675" s="5"/>
@@ -11515,7 +11479,7 @@
         <v>685</v>
       </c>
       <c r="C676" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D676" s="3"/>
       <c r="E676" s="3"/>
@@ -11528,7 +11492,7 @@
         <v>686</v>
       </c>
       <c r="C677" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D677" s="5"/>
       <c r="E677" s="5"/>
@@ -11541,7 +11505,7 @@
         <v>687</v>
       </c>
       <c r="C678" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D678" s="3"/>
       <c r="E678" s="3"/>
@@ -11554,7 +11518,7 @@
         <v>688</v>
       </c>
       <c r="C679" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D679" s="5"/>
       <c r="E679" s="5"/>
@@ -11567,7 +11531,7 @@
         <v>689</v>
       </c>
       <c r="C680" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D680" s="3"/>
       <c r="E680" s="3"/>
@@ -11580,7 +11544,7 @@
         <v>690</v>
       </c>
       <c r="C681" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D681" s="5"/>
       <c r="E681" s="5"/>
@@ -11593,7 +11557,7 @@
         <v>691</v>
       </c>
       <c r="C682" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D682" s="3"/>
       <c r="E682" s="3"/>
@@ -11606,7 +11570,7 @@
         <v>692</v>
       </c>
       <c r="C683" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D683" s="5"/>
       <c r="E683" s="5"/>
@@ -11619,7 +11583,7 @@
         <v>693</v>
       </c>
       <c r="C684" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D684" s="3"/>
       <c r="E684" s="3"/>
@@ -11632,7 +11596,7 @@
         <v>694</v>
       </c>
       <c r="C685" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D685" s="5"/>
       <c r="E685" s="5"/>
@@ -11645,7 +11609,7 @@
         <v>695</v>
       </c>
       <c r="C686" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D686" s="3"/>
       <c r="E686" s="3"/>
@@ -11658,7 +11622,7 @@
         <v>696</v>
       </c>
       <c r="C687" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D687" s="5"/>
       <c r="E687" s="5"/>
@@ -11671,7 +11635,7 @@
         <v>697</v>
       </c>
       <c r="C688" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D688" s="3"/>
       <c r="E688" s="3"/>
@@ -11684,7 +11648,7 @@
         <v>698</v>
       </c>
       <c r="C689" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D689" s="5"/>
       <c r="E689" s="5"/>
@@ -11697,7 +11661,7 @@
         <v>699</v>
       </c>
       <c r="C690" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D690" s="3"/>
       <c r="E690" s="3"/>
@@ -11710,7 +11674,7 @@
         <v>700</v>
       </c>
       <c r="C691" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D691" s="5"/>
       <c r="E691" s="5"/>
@@ -11723,7 +11687,7 @@
         <v>701</v>
       </c>
       <c r="C692" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D692" s="3"/>
       <c r="E692" s="3"/>
@@ -11736,7 +11700,7 @@
         <v>702</v>
       </c>
       <c r="C693" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D693" s="5"/>
       <c r="E693" s="5"/>
@@ -11749,7 +11713,7 @@
         <v>703</v>
       </c>
       <c r="C694" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D694" s="3"/>
       <c r="E694" s="3"/>
@@ -11762,7 +11726,7 @@
         <v>704</v>
       </c>
       <c r="C695" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D695" s="5"/>
       <c r="E695" s="5"/>
@@ -11775,7 +11739,7 @@
         <v>705</v>
       </c>
       <c r="C696" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D696" s="3"/>
       <c r="E696" s="3"/>
@@ -11788,7 +11752,7 @@
         <v>706</v>
       </c>
       <c r="C697" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D697" s="5"/>
       <c r="E697" s="5"/>
@@ -11801,7 +11765,7 @@
         <v>707</v>
       </c>
       <c r="C698" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D698" s="3"/>
       <c r="E698" s="3"/>
@@ -11814,7 +11778,7 @@
         <v>708</v>
       </c>
       <c r="C699" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D699" s="5"/>
       <c r="E699" s="5"/>
@@ -11827,7 +11791,7 @@
         <v>709</v>
       </c>
       <c r="C700" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D700" s="3"/>
       <c r="E700" s="3"/>
@@ -11840,7 +11804,7 @@
         <v>710</v>
       </c>
       <c r="C701" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D701" s="5"/>
       <c r="E701" s="5"/>
@@ -11853,7 +11817,7 @@
         <v>711</v>
       </c>
       <c r="C702" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D702" s="3"/>
       <c r="E702" s="3"/>
@@ -11866,7 +11830,7 @@
         <v>712</v>
       </c>
       <c r="C703" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D703" s="5"/>
       <c r="E703" s="5"/>
@@ -11879,7 +11843,7 @@
         <v>713</v>
       </c>
       <c r="C704" s="4" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D704" s="3"/>
       <c r="E704" s="3"/>
@@ -11892,7 +11856,7 @@
         <v>714</v>
       </c>
       <c r="C705" s="6" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="D705" s="5"/>
       <c r="E705" s="5"/>
@@ -11905,7 +11869,7 @@
         <v>715</v>
       </c>
       <c r="C706" s="4" t="s">
-        <v>615</v>
+        <v>716</v>
       </c>
       <c r="D706" s="3"/>
       <c r="E706" s="3"/>
@@ -11915,10 +11879,10 @@
         <v>706</v>
       </c>
       <c r="B707" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="C707" s="6" t="s">
         <v>716</v>
-      </c>
-      <c r="C707" s="6" t="s">
-        <v>615</v>
       </c>
       <c r="D707" s="5"/>
       <c r="E707" s="5"/>
@@ -11928,10 +11892,10 @@
         <v>707</v>
       </c>
       <c r="B708" s="3" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C708" s="4" t="s">
-        <v>615</v>
+        <v>716</v>
       </c>
       <c r="D708" s="3"/>
       <c r="E708" s="3"/>
@@ -11941,10 +11905,10 @@
         <v>708</v>
       </c>
       <c r="B709" s="5" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C709" s="6" t="s">
-        <v>615</v>
+        <v>716</v>
       </c>
       <c r="D709" s="5"/>
       <c r="E709" s="5"/>
@@ -11954,10 +11918,10 @@
         <v>709</v>
       </c>
       <c r="B710" s="3" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C710" s="4" t="s">
-        <v>615</v>
+        <v>716</v>
       </c>
       <c r="D710" s="3"/>
       <c r="E710" s="3"/>
@@ -11967,10 +11931,10 @@
         <v>710</v>
       </c>
       <c r="B711" s="5" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C711" s="6" t="s">
-        <v>615</v>
+        <v>716</v>
       </c>
       <c r="D711" s="5"/>
       <c r="E711" s="5"/>
@@ -11980,10 +11944,10 @@
         <v>711</v>
       </c>
       <c r="B712" s="3" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C712" s="4" t="s">
-        <v>615</v>
+        <v>716</v>
       </c>
       <c r="D712" s="3"/>
       <c r="E712" s="3"/>
@@ -11993,10 +11957,10 @@
         <v>712</v>
       </c>
       <c r="B713" s="5" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C713" s="6" t="s">
-        <v>615</v>
+        <v>716</v>
       </c>
       <c r="D713" s="5"/>
       <c r="E713" s="5"/>
@@ -12006,10 +11970,10 @@
         <v>713</v>
       </c>
       <c r="B714" s="3" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C714" s="4" t="s">
-        <v>615</v>
+        <v>716</v>
       </c>
       <c r="D714" s="3"/>
       <c r="E714" s="3"/>
@@ -12019,10 +11983,10 @@
         <v>714</v>
       </c>
       <c r="B715" s="5" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C715" s="6" t="s">
-        <v>615</v>
+        <v>716</v>
       </c>
       <c r="D715" s="5"/>
       <c r="E715" s="5"/>
@@ -12032,10 +11996,10 @@
         <v>715</v>
       </c>
       <c r="B716" s="3" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C716" s="4" t="s">
-        <v>615</v>
+        <v>716</v>
       </c>
       <c r="D716" s="3"/>
       <c r="E716" s="3"/>
@@ -12045,10 +12009,10 @@
         <v>716</v>
       </c>
       <c r="B717" s="5" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C717" s="6" t="s">
-        <v>615</v>
+        <v>716</v>
       </c>
       <c r="D717" s="5"/>
       <c r="E717" s="5"/>
@@ -12058,10 +12022,10 @@
         <v>717</v>
       </c>
       <c r="B718" s="3" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C718" s="4" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D718" s="3"/>
       <c r="E718" s="3"/>
@@ -12074,7 +12038,7 @@
         <v>729</v>
       </c>
       <c r="C719" s="6" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D719" s="5"/>
       <c r="E719" s="5"/>
@@ -12087,7 +12051,7 @@
         <v>730</v>
       </c>
       <c r="C720" s="4" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D720" s="3"/>
       <c r="E720" s="3"/>
@@ -12100,7 +12064,7 @@
         <v>731</v>
       </c>
       <c r="C721" s="6" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D721" s="5"/>
       <c r="E721" s="5"/>
@@ -12113,7 +12077,7 @@
         <v>732</v>
       </c>
       <c r="C722" s="4" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D722" s="3"/>
       <c r="E722" s="3"/>
@@ -12126,7 +12090,7 @@
         <v>733</v>
       </c>
       <c r="C723" s="6" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D723" s="5"/>
       <c r="E723" s="5"/>
@@ -12139,7 +12103,7 @@
         <v>734</v>
       </c>
       <c r="C724" s="4" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D724" s="3"/>
       <c r="E724" s="3"/>
@@ -12152,7 +12116,7 @@
         <v>735</v>
       </c>
       <c r="C725" s="6" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D725" s="5"/>
       <c r="E725" s="5"/>
@@ -12165,7 +12129,7 @@
         <v>736</v>
       </c>
       <c r="C726" s="4" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D726" s="3"/>
       <c r="E726" s="3"/>
@@ -12178,7 +12142,7 @@
         <v>737</v>
       </c>
       <c r="C727" s="6" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D727" s="5"/>
       <c r="E727" s="5"/>
@@ -12191,7 +12155,7 @@
         <v>738</v>
       </c>
       <c r="C728" s="4" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D728" s="3"/>
       <c r="E728" s="3"/>
@@ -12204,7 +12168,7 @@
         <v>739</v>
       </c>
       <c r="C729" s="6" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D729" s="5"/>
       <c r="E729" s="5"/>
@@ -12217,7 +12181,7 @@
         <v>740</v>
       </c>
       <c r="C730" s="4" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D730" s="3"/>
       <c r="E730" s="3"/>
@@ -12230,7 +12194,7 @@
         <v>741</v>
       </c>
       <c r="C731" s="6" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D731" s="5"/>
       <c r="E731" s="5"/>
@@ -12243,7 +12207,7 @@
         <v>742</v>
       </c>
       <c r="C732" s="4" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D732" s="3"/>
       <c r="E732" s="3"/>
@@ -12256,7 +12220,7 @@
         <v>743</v>
       </c>
       <c r="C733" s="6" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D733" s="5"/>
       <c r="E733" s="5"/>
@@ -12269,7 +12233,7 @@
         <v>744</v>
       </c>
       <c r="C734" s="4" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D734" s="3"/>
       <c r="E734" s="3"/>
@@ -12282,7 +12246,7 @@
         <v>745</v>
       </c>
       <c r="C735" s="6" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D735" s="5"/>
       <c r="E735" s="5"/>
@@ -12295,7 +12259,7 @@
         <v>746</v>
       </c>
       <c r="C736" s="4" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D736" s="3"/>
       <c r="E736" s="3"/>
@@ -12308,7 +12272,7 @@
         <v>747</v>
       </c>
       <c r="C737" s="6" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D737" s="5"/>
       <c r="E737" s="5"/>
@@ -12321,7 +12285,7 @@
         <v>748</v>
       </c>
       <c r="C738" s="4" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D738" s="3"/>
       <c r="E738" s="3"/>
@@ -12334,7 +12298,7 @@
         <v>749</v>
       </c>
       <c r="C739" s="6" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D739" s="5"/>
       <c r="E739" s="5"/>
@@ -12347,7 +12311,7 @@
         <v>750</v>
       </c>
       <c r="C740" s="4" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D740" s="3"/>
       <c r="E740" s="3"/>
@@ -12360,7 +12324,7 @@
         <v>751</v>
       </c>
       <c r="C741" s="6" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D741" s="5"/>
       <c r="E741" s="5"/>
@@ -12373,7 +12337,7 @@
         <v>752</v>
       </c>
       <c r="C742" s="4" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D742" s="3"/>
       <c r="E742" s="3"/>
@@ -12386,7 +12350,7 @@
         <v>753</v>
       </c>
       <c r="C743" s="6" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D743" s="5"/>
       <c r="E743" s="5"/>
@@ -12399,7 +12363,7 @@
         <v>754</v>
       </c>
       <c r="C744" s="4" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D744" s="3"/>
       <c r="E744" s="3"/>
@@ -12412,7 +12376,7 @@
         <v>755</v>
       </c>
       <c r="C745" s="6" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D745" s="5"/>
       <c r="E745" s="5"/>
@@ -12425,7 +12389,7 @@
         <v>756</v>
       </c>
       <c r="C746" s="4" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D746" s="3"/>
       <c r="E746" s="3"/>
@@ -12438,166 +12402,10 @@
         <v>757</v>
       </c>
       <c r="C747" s="6" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D747" s="5"/>
       <c r="E747" s="5"/>
-    </row>
-    <row r="748" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A748" s="3">
-        <v>747</v>
-      </c>
-      <c r="B748" s="3" t="s">
-        <v>758</v>
-      </c>
-      <c r="C748" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="D748" s="3"/>
-      <c r="E748" s="3"/>
-    </row>
-    <row r="749" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A749" s="5">
-        <v>748</v>
-      </c>
-      <c r="B749" s="5" t="s">
-        <v>759</v>
-      </c>
-      <c r="C749" s="6" t="s">
-        <v>728</v>
-      </c>
-      <c r="D749" s="5"/>
-      <c r="E749" s="5"/>
-    </row>
-    <row r="750" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A750" s="3">
-        <v>749</v>
-      </c>
-      <c r="B750" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="C750" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="D750" s="3"/>
-      <c r="E750" s="3"/>
-    </row>
-    <row r="751" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A751" s="5">
-        <v>750</v>
-      </c>
-      <c r="B751" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="C751" s="6" t="s">
-        <v>728</v>
-      </c>
-      <c r="D751" s="5"/>
-      <c r="E751" s="5"/>
-    </row>
-    <row r="752" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A752" s="3">
-        <v>751</v>
-      </c>
-      <c r="B752" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="C752" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="D752" s="3"/>
-      <c r="E752" s="3"/>
-    </row>
-    <row r="753" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A753" s="5">
-        <v>752</v>
-      </c>
-      <c r="B753" s="5" t="s">
-        <v>763</v>
-      </c>
-      <c r="C753" s="6" t="s">
-        <v>728</v>
-      </c>
-      <c r="D753" s="5"/>
-      <c r="E753" s="5"/>
-    </row>
-    <row r="754" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A754" s="3">
-        <v>753</v>
-      </c>
-      <c r="B754" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="C754" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="D754" s="3"/>
-      <c r="E754" s="3"/>
-    </row>
-    <row r="755" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A755" s="5">
-        <v>754</v>
-      </c>
-      <c r="B755" s="5" t="s">
-        <v>765</v>
-      </c>
-      <c r="C755" s="6" t="s">
-        <v>728</v>
-      </c>
-      <c r="D755" s="5"/>
-      <c r="E755" s="5"/>
-    </row>
-    <row r="756" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A756" s="3">
-        <v>755</v>
-      </c>
-      <c r="B756" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="C756" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="D756" s="3"/>
-      <c r="E756" s="3"/>
-    </row>
-    <row r="757" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A757" s="5">
-        <v>756</v>
-      </c>
-      <c r="B757" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="C757" s="6" t="s">
-        <v>728</v>
-      </c>
-      <c r="D757" s="5"/>
-      <c r="E757" s="5"/>
-    </row>
-    <row r="758" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A758" s="3">
-        <v>757</v>
-      </c>
-      <c r="B758" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="C758" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="D758" s="3"/>
-      <c r="E758" s="3"/>
-    </row>
-    <row r="759" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A759" s="5">
-        <v>758</v>
-      </c>
-      <c r="B759" s="5" t="s">
-        <v>769</v>
-      </c>
-      <c r="C759" s="6" t="s">
-        <v>728</v>
-      </c>
-      <c r="D759" s="5"/>
-      <c r="E759" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
